--- a/data/employees/EMP067/AST-EMP067-06.xlsx
+++ b/data/employees/EMP067/AST-EMP067-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Resource Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System Resource Utilization - Riley Patel (IT)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Riley Patel | Role: Lead | Location: Austin | Date: 2025-03-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>92</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CPU %</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Memory %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Disk %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Network (Mbps)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROD-APP-01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>76</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PROD-SQL-02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>81</v>
-      </c>
-      <c r="D6" t="n">
-        <v>88</v>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>880</v>
+        <v>84</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>Section 1: Department KPI performance. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV-WEB-01</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40</v>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEST-API-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D8" t="n">
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>88</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>98</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>83</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>65</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>98</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>91</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>95</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>79</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>95</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>68</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>70</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>87</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>90</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>62</v>
       </c>
-      <c r="E8" t="n">
-        <v>450</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>87</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>92</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>78</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp067 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>64</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP067</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP067 contributes to ast emp067 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>